--- a/excel_ai/templates/MTInputs_template.xlsx
+++ b/excel_ai/templates/MTInputs_template.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
       <c r="A1" s="5" t="n"/>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>MTInputs template - row structure copied exactly from legacy CPAT MTInputs</t>
+          <t>MTInputs template - row structure copied exactly from legacy CPAT MTInputs (CPAT 1.0pre_465)</t>
         </is>
       </c>
       <c r="C1" s="5" t="n"/>
@@ -498,7 +498,7 @@
       <c r="A3" s="7" t="n"/>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Rows must match legacy exactly. Green (EBF1DE) = used by module; grey (F2F2F2) = unused. See NORMS.md section 4.</t>
+          <t>Rows must match legacy 465 exactly. Column H: the names of the codes map (tab Inputs; legacy name kept there). See NORMS.md section 4.</t>
         </is>
       </c>
       <c r="C3" s="7" t="n"/>
@@ -644,7 +644,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>ScenarioStatus</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
@@ -669,7 +673,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H12" s="8" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>ScenarioName</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
@@ -723,7 +731,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>ScenarioStatusMacro</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
@@ -748,7 +760,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>ScenarioParamOverride</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
@@ -1621,7 +1637,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>D_FeebateIntro</t>
+          <t>FeebateIntro</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1658,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>D_FeebateOutro</t>
+          <t>FeebateOutro</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1690,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Start_Pow</t>
+          <t>Feb_Level_Start_Pow</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1715,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Start_Trans</t>
+          <t>Feb_Level_Start_Trans</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1740,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Start_Res</t>
+          <t>Feb_Level_Start_Res</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1765,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Start_Ind</t>
+          <t>Feb_Level_Start_Ind</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1797,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Target_Pow</t>
+          <t>Feb_Level_Target_Pow</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1822,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Target_Trans</t>
+          <t>Feb_Level_Target_Trans</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1847,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Target_Res</t>
+          <t>Feb_Level_Target_Res</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1872,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>D_Feb_Level_Target_Ind</t>
+          <t>Feb_Level_Target_Ind</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1902,11 @@
       <c r="G66" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>FbCovPow</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="8" t="inlineStr">
@@ -1903,7 +1923,11 @@
       <c r="G67" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H67" s="8" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>FbCovRod</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="8" t="inlineStr">
@@ -1920,7 +1944,11 @@
       <c r="G68" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>FbCovRal</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="8" t="inlineStr">
@@ -1937,7 +1965,11 @@
       <c r="G69" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>FbCovAvi</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="8" t="inlineStr">
@@ -1954,7 +1986,11 @@
       <c r="G70" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H70" s="8" t="n"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>FbCovNav</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="8" t="inlineStr">
@@ -1975,7 +2011,11 @@
       <c r="G71" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>FbCovRes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="8" t="inlineStr">
@@ -1992,7 +2032,11 @@
       <c r="G72" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H72" s="8" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>FbCovFoo</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="8" t="inlineStr">
@@ -2009,7 +2053,11 @@
       <c r="G73" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>FbCovSrv</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="8" t="inlineStr">
@@ -2026,7 +2074,11 @@
       <c r="G74" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>FbCovMch</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="8" t="inlineStr">
@@ -2043,7 +2095,11 @@
       <c r="G75" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H75" s="8" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>FbCovIrn</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="8" t="inlineStr">
@@ -2060,7 +2116,11 @@
       <c r="G76" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H76" s="8" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>FbCovNfm</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
@@ -2077,7 +2137,11 @@
       <c r="G77" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H77" s="8" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>FbCovMac</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
@@ -2094,7 +2158,11 @@
       <c r="G78" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H78" s="8" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>FbCovCem</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
@@ -2111,7 +2179,11 @@
       <c r="G79" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H79" s="8" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>FbCovOmn</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
@@ -2128,7 +2200,11 @@
       <c r="G80" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H80" s="8" t="n"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>FbCovCst</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
@@ -2145,7 +2221,11 @@
       <c r="G81" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>FbCovFtr</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
@@ -2162,7 +2242,11 @@
       <c r="G82" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H82" s="8" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>FbCovOen</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="1" t="inlineStr">
@@ -2192,7 +2276,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>D_NewETS</t>
+          <t>NewETS</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2297,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>D_ETSChangeRelStart</t>
+          <t>ETSChangeRelStart</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2318,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>D_ETSChangeRelTarget</t>
+          <t>ETSChangeRelTarget</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2343,7 @@
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>D_ETSCapCont</t>
+          <t>ETSCapCont</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2364,7 @@
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>D_ETSIntro</t>
+          <t>ETSIntro</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2385,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>D_ETSOutro</t>
+          <t>ETSOutro</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2406,7 @@
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>D_ETSAuctStart</t>
+          <t>ETSAuctStart</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2427,7 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>D_ETSAuctTarget</t>
+          <t>ETSAuctTarget</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2452,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>D_ETSAuctCont</t>
+          <t>ETSAuctCont</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2477,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>D_ETSPriceOverride</t>
+          <t>ETSPriceOverride</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2509,7 @@
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>D_ETSVolatility</t>
+          <t>ETSVolatility</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2534,7 @@
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>D_ETSVolImpact</t>
+          <t>ETSVolImpact</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2555,7 @@
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>D_ETSCTRisk</t>
+          <t>ETSCTRisk</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2585,11 @@
       <c r="G99" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovPow</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="8" t="inlineStr">
@@ -2518,7 +2606,11 @@
       <c r="G100" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H100" s="8" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovRod</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="8" t="inlineStr">
@@ -2535,7 +2627,11 @@
       <c r="G101" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H101" s="8" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovRal</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="8" t="inlineStr">
@@ -2552,7 +2648,11 @@
       <c r="G102" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H102" s="8" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovAvi</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="8" t="inlineStr">
@@ -2569,7 +2669,11 @@
       <c r="G103" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H103" s="8" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovNav</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="8" t="inlineStr">
@@ -2590,7 +2694,11 @@
       <c r="G104" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H104" s="8" t="n"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovRes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="8" t="inlineStr">
@@ -2607,7 +2715,11 @@
       <c r="G105" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H105" s="8" t="n"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovFoo</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="8" t="inlineStr">
@@ -2624,7 +2736,11 @@
       <c r="G106" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H106" s="8" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovSrv</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="8" t="inlineStr">
@@ -2641,7 +2757,11 @@
       <c r="G107" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H107" s="8" t="n"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovMch</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="8" t="inlineStr">
@@ -2658,7 +2778,11 @@
       <c r="G108" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H108" s="8" t="n"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovIrn</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="8" t="inlineStr">
@@ -2675,7 +2799,11 @@
       <c r="G109" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H109" s="8" t="n"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovNfm</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="B110" s="8" t="inlineStr">
@@ -2692,7 +2820,11 @@
       <c r="G110" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H110" s="8" t="n"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovMac</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="8" t="inlineStr">
@@ -2709,7 +2841,11 @@
       <c r="G111" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H111" s="8" t="n"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovCem</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="8" t="inlineStr">
@@ -2726,7 +2862,11 @@
       <c r="G112" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H112" s="8" t="n"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovOmn</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="8" t="inlineStr">
@@ -2743,7 +2883,11 @@
       <c r="G113" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H113" s="8" t="n"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovCst</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="8" t="inlineStr">
@@ -2760,7 +2904,11 @@
       <c r="G114" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H114" s="8" t="n"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovFtr</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="8" t="inlineStr">
@@ -2777,7 +2925,11 @@
       <c r="G115" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H115" s="8" t="n"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>ETSCovOen</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="B116" s="1" t="inlineStr">
@@ -2801,7 +2953,11 @@
       <c r="G117" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H117" s="8" t="n"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>CBAMProcMch</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="8" t="inlineStr">
@@ -2818,7 +2974,11 @@
       <c r="G118" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H118" s="8" t="n"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>CBAMProcIrn</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="B119" s="8" t="inlineStr">
@@ -2835,7 +2995,11 @@
       <c r="G119" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H119" s="8" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>CBAMProcNfm</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="B120" s="8" t="inlineStr">
@@ -2852,7 +3016,11 @@
       <c r="G120" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H120" s="8" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>CBAMProcMac</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="8" t="inlineStr">
@@ -2869,7 +3037,11 @@
       <c r="G121" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H121" s="8" t="n"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>CBAMProcCem</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="1" t="inlineStr">
@@ -3294,7 +3466,11 @@
       <c r="G140" s="8" t="n">
         <v>2027</v>
       </c>
-      <c r="H140" s="8" t="n"/>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>FprIntro</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="8" t="inlineStr">
@@ -3311,7 +3487,11 @@
       <c r="G141" s="8" t="n">
         <v>2035</v>
       </c>
-      <c r="H141" s="8" t="n"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>FprOutro</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="8" t="inlineStr">
@@ -3328,7 +3508,11 @@
       <c r="G142" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H142" s="8" t="n"/>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>FprStartCoaPow</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="8" t="inlineStr">
@@ -3345,7 +3529,11 @@
       <c r="G143" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H143" s="8" t="n"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>FprStartCoaRes</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="8" t="inlineStr">
@@ -3362,7 +3550,11 @@
       <c r="G144" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H144" s="8" t="n"/>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>FprStartCoaInd</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="8" t="inlineStr">
@@ -3379,7 +3571,11 @@
       <c r="G145" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H145" s="8" t="n"/>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>FprStartNgaPow</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="B146" s="8" t="inlineStr">
@@ -3396,7 +3592,11 @@
       <c r="G146" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H146" s="8" t="n"/>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>FprStartNgaRes</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="8" t="inlineStr">
@@ -3413,7 +3613,11 @@
       <c r="G147" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H147" s="8" t="n"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>FprStartNgaInd</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="B148" s="8" t="inlineStr">
@@ -3430,7 +3634,11 @@
       <c r="G148" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H148" s="8" t="n"/>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>FprStartEcyRes</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="8" t="inlineStr">
@@ -3447,7 +3655,11 @@
       <c r="G149" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H149" s="8" t="n"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>FprStartEcyInd</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="8" t="inlineStr">
@@ -3464,7 +3676,11 @@
       <c r="G150" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H150" s="8" t="n"/>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>FprStartGsoAll</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="8" t="inlineStr">
@@ -3481,7 +3697,11 @@
       <c r="G151" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H151" s="8" t="n"/>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>FprStartDieAll</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="8" t="inlineStr">
@@ -3498,7 +3718,11 @@
       <c r="G152" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H152" s="8" t="n"/>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>FprStartLpgAll</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="8" t="inlineStr">
@@ -3515,7 +3739,11 @@
       <c r="G153" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H153" s="8" t="n"/>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>FprStartKerAll</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="8" t="inlineStr">
@@ -3532,7 +3760,11 @@
       <c r="G154" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H154" s="8" t="n"/>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>FprStartOopAll</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="B155" s="8" t="inlineStr">
@@ -3549,7 +3781,11 @@
       <c r="G155" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H155" s="8" t="n"/>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>FprStartBioAll</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="B156" s="8" t="inlineStr">
@@ -3566,7 +3802,11 @@
       <c r="G156" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H156" s="8" t="n"/>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalCoaPow</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="8" t="inlineStr">
@@ -3583,7 +3823,11 @@
       <c r="G157" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H157" s="8" t="n"/>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalCoaRes</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="8" t="inlineStr">
@@ -3600,7 +3844,11 @@
       <c r="G158" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H158" s="8" t="n"/>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalCoaInd</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="8" t="inlineStr">
@@ -3617,7 +3865,11 @@
       <c r="G159" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H159" s="8" t="n"/>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalNgaPow</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="8" t="inlineStr">
@@ -3634,7 +3886,11 @@
       <c r="G160" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H160" s="8" t="n"/>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalNgaRes</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="B161" s="8" t="inlineStr">
@@ -3651,7 +3907,11 @@
       <c r="G161" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H161" s="8" t="n"/>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalNgaInd</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="B162" s="8" t="inlineStr">
@@ -3668,7 +3928,11 @@
       <c r="G162" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H162" s="8" t="n"/>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalEcyRes</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="B163" s="8" t="inlineStr">
@@ -3685,7 +3949,11 @@
       <c r="G163" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H163" s="8" t="n"/>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalEcyInd</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="8" t="inlineStr">
@@ -3702,7 +3970,11 @@
       <c r="G164" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H164" s="8" t="n"/>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalGsoAll</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="B165" s="8" t="inlineStr">
@@ -3719,7 +3991,11 @@
       <c r="G165" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H165" s="8" t="n"/>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalDieAll</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="B166" s="8" t="inlineStr">
@@ -3736,7 +4012,11 @@
       <c r="G166" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H166" s="8" t="n"/>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalLpgAll</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="8" t="inlineStr">
@@ -3753,7 +4033,11 @@
       <c r="G167" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H167" s="8" t="n"/>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalKerAll</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="B168" s="8" t="inlineStr">
@@ -3770,7 +4054,11 @@
       <c r="G168" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H168" s="8" t="n"/>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalOopAll</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="B169" s="8" t="inlineStr">
@@ -3787,7 +4075,11 @@
       <c r="G169" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H169" s="8" t="n"/>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>FprFinalBioAll</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="B170" s="8" t="inlineStr">
@@ -3808,7 +4100,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H170" s="8" t="n"/>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitCoaPow</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="B171" s="8" t="inlineStr">
@@ -3829,7 +4125,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H171" s="8" t="n"/>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitCoaRes</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="B172" s="8" t="inlineStr">
@@ -3850,7 +4150,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H172" s="8" t="n"/>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitCoaInd</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="B173" s="8" t="inlineStr">
@@ -3871,7 +4175,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H173" s="8" t="n"/>
+      <c r="H173" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitNgaPow</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="B174" s="8" t="inlineStr">
@@ -3892,7 +4200,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H174" s="8" t="n"/>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitNgaRes</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="8" t="inlineStr">
@@ -3913,7 +4225,11 @@
           <t>$/GJ</t>
         </is>
       </c>
-      <c r="H175" s="8" t="n"/>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitNgaInd</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="B176" s="8" t="inlineStr">
@@ -3934,7 +4250,11 @@
           <t>$/kwh</t>
         </is>
       </c>
-      <c r="H176" s="8" t="n"/>
+      <c r="H176" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitEcyRes</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="8" t="inlineStr">
@@ -3955,7 +4275,11 @@
           <t>$/kwh</t>
         </is>
       </c>
-      <c r="H177" s="8" t="n"/>
+      <c r="H177" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitEcyInd</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="B178" s="8" t="inlineStr">
@@ -3976,7 +4300,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H178" s="8" t="n"/>
+      <c r="H178" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitGsoAll</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="B179" s="8" t="inlineStr">
@@ -3997,7 +4325,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H179" s="8" t="n"/>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitDieAll</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="B180" s="8" t="inlineStr">
@@ -4018,7 +4350,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H180" s="8" t="n"/>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitLpgAll</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="B181" s="8" t="inlineStr">
@@ -4039,7 +4375,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H181" s="8" t="n"/>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitKerAll</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="B182" s="8" t="inlineStr">
@@ -4060,7 +4400,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H182" s="8" t="n"/>
+      <c r="H182" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitOopAll</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="B183" s="8" t="inlineStr">
@@ -4081,7 +4425,11 @@
           <t>$/liter</t>
         </is>
       </c>
-      <c r="H183" s="8" t="n"/>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>FprUnitBioAll</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="B184" s="1" t="inlineStr">
@@ -7613,7 +7961,7 @@
     <row r="329">
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>VSL elasticity source</t>
+          <t>Discount rate selection</t>
         </is>
       </c>
       <c r="C329" s="8" t="inlineStr">
@@ -7625,24 +7973,24 @@
       <c r="E329" s="8" t="n"/>
       <c r="F329" s="8" t="inlineStr">
         <is>
-          <t>0x17</t>
+          <t>3% (Robinson 2019)</t>
         </is>
       </c>
       <c r="G329" s="8" t="inlineStr">
         <is>
-          <t>Income group</t>
+          <t>3% (Robinson 2019)</t>
         </is>
       </c>
       <c r="H329" s="8" t="inlineStr">
         <is>
-          <t>VslElSource</t>
+          <t>DiscSel</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="B330" s="8" t="inlineStr">
         <is>
-          <t>VSL elasticity (where manual source)</t>
+          <t>Discount rate (where manual source)</t>
         </is>
       </c>
       <c r="C330" s="8" t="inlineStr">
@@ -7652,110 +8000,104 @@
       </c>
       <c r="D330" s="8" t="n"/>
       <c r="E330" s="8" t="n"/>
-      <c r="F330" s="8" t="inlineStr">
-        <is>
-          <t>0x17</t>
-        </is>
+      <c r="F330" s="8" t="n">
+        <v>0.03</v>
       </c>
       <c r="G330" s="8" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="H330" s="8" t="inlineStr">
         <is>
-          <t>VslEl</t>
+          <t>DiscRate</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="B331" s="8" t="inlineStr">
-        <is>
-          <t>Discount rate selection</t>
-        </is>
-      </c>
-      <c r="C331" s="8" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="D331" s="8" t="n"/>
-      <c r="E331" s="8" t="n"/>
-      <c r="F331" s="8" t="inlineStr">
-        <is>
-          <t>3% (Robinson 2019)</t>
-        </is>
-      </c>
-      <c r="G331" s="8" t="inlineStr">
-        <is>
-          <t>3% (Robinson 2019)</t>
-        </is>
-      </c>
-      <c r="H331" s="8" t="inlineStr">
-        <is>
-          <t>DiscSel</t>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t>Other assumptions: air pollution module</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t>Discount rate (where manual source)</t>
+          <t>Number of working days per month</t>
         </is>
       </c>
       <c r="C332" s="8" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D332" s="8" t="n"/>
       <c r="E332" s="8" t="n"/>
       <c r="F332" s="8" t="n">
-        <v>0.03</v>
+        <v>20</v>
       </c>
       <c r="G332" s="8" t="n">
-        <v>0.03</v>
+        <v>20</v>
       </c>
       <c r="H332" s="8" t="inlineStr">
         <is>
-          <t>DiscRate</t>
+          <t>WorkDays</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t>Other assumptions: air pollution module</t>
+      <c r="B333" s="8" t="inlineStr">
+        <is>
+          <t>Labor share of GDP, default value</t>
+        </is>
+      </c>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="n"/>
+      <c r="E333" s="8" t="n"/>
+      <c r="F333" s="8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G333" s="8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H333" s="8" t="inlineStr">
+        <is>
+          <t>ApLabSh</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="B334" s="8" t="inlineStr">
         <is>
-          <t>Number of working days per month</t>
+          <t>Max % of households using solid fuels</t>
         </is>
       </c>
       <c r="C334" s="8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D334" s="8" t="n"/>
       <c r="E334" s="8" t="n"/>
       <c r="F334" s="8" t="n">
-        <v>20</v>
+        <v>0.99</v>
       </c>
       <c r="G334" s="8" t="n">
-        <v>20</v>
+        <v>0.99</v>
       </c>
       <c r="H334" s="8" t="inlineStr">
         <is>
-          <t>WorkDays</t>
+          <t>ApMaxSs</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Labor share of GDP, default value</t>
+          <t>Leakage converted into % HH using solid fuels</t>
         </is>
       </c>
       <c r="C335" s="8" t="inlineStr">
@@ -7766,540 +8108,532 @@
       <c r="D335" s="8" t="n"/>
       <c r="E335" s="8" t="n"/>
       <c r="F335" s="8" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G335" s="8" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="H335" s="8" t="inlineStr">
         <is>
-          <t>ApLabSh</t>
+          <t>ApLeakHh</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="B336" s="8" t="inlineStr">
         <is>
-          <t>Max % of households using solid fuels</t>
+          <t>Apply cessation lag when discounting averted deaths</t>
         </is>
       </c>
       <c r="C336" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="D336" s="8" t="n"/>
       <c r="E336" s="8" t="n"/>
-      <c r="F336" s="8" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="G336" s="8" t="n">
-        <v>0.99</v>
+      <c r="F336" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G336" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="H336" s="8" t="inlineStr">
         <is>
-          <t>ApMaxSs</t>
+          <t>ApCessLag</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="B337" s="8" t="inlineStr">
-        <is>
-          <t>Leakage converted into % HH using solid fuels</t>
-        </is>
-      </c>
-      <c r="C337" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D337" s="8" t="n"/>
-      <c r="E337" s="8" t="n"/>
-      <c r="F337" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G337" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H337" s="8" t="inlineStr">
-        <is>
-          <t>ApLeakHh</t>
+      <c r="B337" s="1" t="inlineStr">
+        <is>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="B338" s="8" t="inlineStr">
         <is>
-          <t>Apply cessation lag when discounting averted deaths</t>
+          <t>Engineering or elasticity model</t>
         </is>
       </c>
       <c r="C338" s="8" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>option</t>
         </is>
       </c>
       <c r="D338" s="8" t="n"/>
       <c r="E338" s="8" t="n"/>
       <c r="F338" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Elasticity</t>
         </is>
       </c>
       <c r="G338" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="H338" s="8" t="inlineStr">
         <is>
-          <t>ApCessLag</t>
+          <t>TrModel</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Power Sector</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="B340" s="8" t="inlineStr">
         <is>
-          <t>Engineering or elasticity model</t>
+          <t>Power Rebate</t>
         </is>
       </c>
       <c r="C340" s="8" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="D340" s="8" t="n"/>
       <c r="E340" s="8" t="n"/>
       <c r="F340" s="8" t="inlineStr">
         <is>
-          <t>Elasticity</t>
+          <t>No*</t>
         </is>
       </c>
       <c r="G340" s="8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>No*</t>
         </is>
       </c>
       <c r="H340" s="8" t="inlineStr">
         <is>
-          <t>TrModel</t>
+          <t>PowerRebates</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="B341" s="1" t="inlineStr">
-        <is>
-          <t>Power Sector</t>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Power price: portion of cost change passed-on:</t>
+        </is>
+      </c>
+      <c r="C341" s="8" t="n"/>
+      <c r="D341" s="8" t="n"/>
+      <c r="E341" s="8" t="n"/>
+      <c r="F341" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H341" s="8" t="inlineStr">
+        <is>
+          <t>PowerSectorPriceChangePassOn</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="B342" s="8" t="inlineStr">
         <is>
-          <t>Power Rebate</t>
+          <t>Year of interest for power sector costs</t>
         </is>
       </c>
       <c r="C342" s="8" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>year</t>
         </is>
       </c>
       <c r="D342" s="8" t="n"/>
       <c r="E342" s="8" t="n"/>
-      <c r="F342" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
-      </c>
-      <c r="G342" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
+      <c r="F342" s="8" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G342" s="8" t="n">
+        <v>2030</v>
       </c>
       <c r="H342" s="8" t="inlineStr">
         <is>
-          <t>PowerRebates</t>
+          <t>CostBreakdownYear</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Power price: portion of cost change passed-on:</t>
-        </is>
-      </c>
-      <c r="C343" s="8" t="n"/>
+          <t>Estimate economy-wide or sectoral power demand?</t>
+        </is>
+      </c>
+      <c r="C343" s="8" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
       <c r="D343" s="8" t="n"/>
       <c r="E343" s="8" t="n"/>
-      <c r="F343" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G343" s="8" t="n">
-        <v>1</v>
+      <c r="F343" s="8" t="inlineStr">
+        <is>
+          <t>Economy-wide</t>
+        </is>
+      </c>
+      <c r="G343" s="8" t="inlineStr">
+        <is>
+          <t>Economy-wide</t>
+        </is>
       </c>
       <c r="H343" s="8" t="inlineStr">
         <is>
-          <t>PowerSectorPriceChangePassOn</t>
+          <t>ElasticityModel</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="B344" s="8" t="inlineStr">
         <is>
-          <t>Year of interest for power sector costs</t>
+          <t>k Parameter dispatch</t>
         </is>
       </c>
       <c r="C344" s="8" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>coefficient</t>
         </is>
       </c>
       <c r="D344" s="8" t="n"/>
       <c r="E344" s="8" t="n"/>
       <c r="F344" s="8" t="n">
-        <v>2030</v>
+        <v>2</v>
       </c>
       <c r="G344" s="8" t="n">
-        <v>2030</v>
+        <v>2</v>
       </c>
       <c r="H344" s="8" t="inlineStr">
         <is>
-          <t>CostBreakdownYear</t>
+          <t>kDispatch</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Estimate economy-wide or sectoral power demand?</t>
+          <t>k Parameter investment</t>
         </is>
       </c>
       <c r="C345" s="8" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>coefficient</t>
         </is>
       </c>
       <c r="D345" s="8" t="n"/>
       <c r="E345" s="8" t="n"/>
-      <c r="F345" s="8" t="inlineStr">
-        <is>
-          <t>Economy-wide</t>
-        </is>
-      </c>
-      <c r="G345" s="8" t="inlineStr">
-        <is>
-          <t>Economy-wide</t>
-        </is>
+      <c r="F345" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G345" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="H345" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ElasticityModel </t>
+          <t>kInvestment</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t>k Parameter dispatch</t>
-        </is>
-      </c>
-      <c r="C346" s="8" t="inlineStr">
-        <is>
-          <t>coefficient</t>
-        </is>
-      </c>
+          <t>Minimum WACC</t>
+        </is>
+      </c>
+      <c r="C346" s="8" t="n"/>
       <c r="D346" s="8" t="n"/>
       <c r="E346" s="8" t="n"/>
       <c r="F346" s="8" t="n">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="G346" s="8" t="n">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="H346" s="8" t="inlineStr">
         <is>
-          <t>kDispatch</t>
+          <t>MinimumWACC</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>k Parameter investment</t>
+          <t>Use old or new generation costs in elasticity model?</t>
         </is>
       </c>
       <c r="C347" s="8" t="inlineStr">
         <is>
-          <t>coefficient</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="D347" s="8" t="n"/>
       <c r="E347" s="8" t="n"/>
-      <c r="F347" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G347" s="8" t="n">
-        <v>2</v>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>New*</t>
+        </is>
+      </c>
+      <c r="G347" s="8" t="inlineStr">
+        <is>
+          <t>New*</t>
+        </is>
       </c>
       <c r="H347" s="8" t="inlineStr">
         <is>
-          <t>kInvestment</t>
+          <t>PowGenCostsOldNew</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="B348" s="8" t="inlineStr">
         <is>
-          <t>Minimum WACC</t>
+          <t>Hydro retirement rate set to zero</t>
         </is>
       </c>
       <c r="C348" s="8" t="n"/>
       <c r="D348" s="8" t="n"/>
       <c r="E348" s="8" t="n"/>
-      <c r="F348" s="8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G348" s="8" t="n">
-        <v>0.01</v>
+      <c r="F348" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G348" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="H348" s="8" t="inlineStr">
         <is>
-          <t>MinimumWACC</t>
+          <t>HydroDoesntRetire</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Use old or new generation costs in elasticity model?</t>
-        </is>
-      </c>
-      <c r="C349" s="8" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
+          <t>Minimum (post subsidy) generation cost $/kwh real</t>
+        </is>
+      </c>
+      <c r="C349" s="8" t="n"/>
       <c r="D349" s="8" t="n"/>
       <c r="E349" s="8" t="n"/>
-      <c r="F349" s="8" t="inlineStr">
-        <is>
-          <t>New*</t>
-        </is>
-      </c>
-      <c r="G349" s="8" t="inlineStr">
-        <is>
-          <t>New*</t>
-        </is>
+      <c r="F349" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G349" s="8" t="n">
+        <v>0.01</v>
       </c>
       <c r="H349" s="8" t="inlineStr">
         <is>
-          <t>PowGenCostsOldNew</t>
+          <t>MinPostSubsidyPowerPrice</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="B350" s="8" t="inlineStr">
-        <is>
-          <t>Hydro retirement rate set to zero</t>
-        </is>
-      </c>
-      <c r="C350" s="8" t="n"/>
-      <c r="D350" s="8" t="n"/>
-      <c r="E350" s="8" t="n"/>
-      <c r="F350" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G350" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H350" s="8" t="inlineStr">
-        <is>
-          <t>HydroDoesntRetire</t>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t>RE Subsidies</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Minimum (post subsidy) generation cost $/kwh real</t>
-        </is>
-      </c>
-      <c r="C351" s="8" t="n"/>
+          <t>Treat over/underestimate of supply costs as subsidy/tax</t>
+        </is>
+      </c>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
       <c r="D351" s="8" t="n"/>
       <c r="E351" s="8" t="n"/>
-      <c r="F351" s="8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G351" s="8" t="n">
-        <v>0.01</v>
+      <c r="F351" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G351" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="H351" s="8" t="inlineStr">
         <is>
-          <t>MinPostSubsidyPowerPrice</t>
+          <t>SupplyCostDeltaSubsidy</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="B352" s="1" t="inlineStr">
-        <is>
-          <t>RE Subsidies</t>
+      <c r="B352" s="8" t="inlineStr">
+        <is>
+          <t>Baseline renewable energy subsidy, $/kwh nom</t>
+        </is>
+      </c>
+      <c r="C352" s="8" t="inlineStr">
+        <is>
+          <t>$/kwh nom</t>
+        </is>
+      </c>
+      <c r="D352" s="8" t="n"/>
+      <c r="E352" s="8" t="n"/>
+      <c r="F352" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H352" s="8" t="inlineStr">
+        <is>
+          <t>RenewableSubsidyBL</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Treat over/underestimate of supply costs as subsidy/tax</t>
+          <t>New renewable energy subsidy, $/kwh nom</t>
         </is>
       </c>
       <c r="C353" s="8" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>$/kwh nom</t>
         </is>
       </c>
       <c r="D353" s="8" t="n"/>
       <c r="E353" s="8" t="n"/>
-      <c r="F353" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G353" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="F353" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H353" s="8" t="inlineStr">
         <is>
-          <t>SupplyCostDeltaSubsidy</t>
+          <t>RenSubsidyAddUSDkwh</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="B354" s="8" t="inlineStr">
         <is>
-          <t>Baseline renewable energy subsidy, $/kwh nom</t>
+          <t>New renewable energy subsidy, phaseout</t>
         </is>
       </c>
       <c r="C354" s="8" t="inlineStr">
         <is>
-          <t>$/kwh nom</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D354" s="8" t="n"/>
       <c r="E354" s="8" t="n"/>
       <c r="F354" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G354" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H354" s="8" t="inlineStr">
         <is>
-          <t>RenewableSubsidyBL</t>
+          <t>RenSubsidyAddPhaseoutYrs</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>New renewable energy subsidy, $/kwh nom</t>
+          <t>Apply additional RE subsidy to hydroelectric power?</t>
         </is>
       </c>
       <c r="C355" s="8" t="inlineStr">
         <is>
-          <t>$/kwh nom</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="D355" s="8" t="n"/>
       <c r="E355" s="8" t="n"/>
-      <c r="F355" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G355" s="8" t="n">
-        <v>0</v>
+      <c r="F355" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G355" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="H355" s="8" t="inlineStr">
         <is>
-          <t>RenSubsidyAddUSDkwh</t>
+          <t>RenewableSubsidyHydro</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="B356" s="8" t="inlineStr">
-        <is>
-          <t>New renewable energy subsidy, phaseout</t>
-        </is>
-      </c>
-      <c r="C356" s="8" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D356" s="8" t="n"/>
-      <c r="E356" s="8" t="n"/>
-      <c r="F356" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G356" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H356" s="8" t="inlineStr">
-        <is>
-          <t>RenSubsidyAddPhaseoutYrs</t>
+      <c r="B356" s="1" t="inlineStr">
+        <is>
+          <t>Electrical Generation Scale-up limits</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Apply additional RE subsidy to hydroelectric power?</t>
-        </is>
-      </c>
-      <c r="C357" s="8" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
+          <t>Max new investment in coal/gas/hyd as a percentage of total generation</t>
+        </is>
+      </c>
+      <c r="C357" s="8" t="n"/>
       <c r="D357" s="8" t="n"/>
       <c r="E357" s="8" t="n"/>
-      <c r="F357" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G357" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="F357" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G357" s="8" t="n">
+        <v>0.05</v>
       </c>
       <c r="H357" s="8" t="inlineStr">
         <is>
-          <t>RenewableSubsidyHydro</t>
+          <t>MaxNonVREAsPCOfTotalGen</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="B358" s="1" t="inlineStr">
-        <is>
-          <t>Electrical Generation Scale-up limits</t>
+      <c r="B358" s="8" t="inlineStr">
+        <is>
+          <t>Max new investment oil/nucl/ore/bio as a percentage of total generation</t>
+        </is>
+      </c>
+      <c r="C358" s="8" t="n"/>
+      <c r="D358" s="8" t="n"/>
+      <c r="E358" s="8" t="n"/>
+      <c r="F358" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G358" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H358" s="8" t="inlineStr">
+        <is>
+          <t>MaxNonNucOreBioAsPCOfTotalGen</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Max new investment in coal/gas/hyd as a percentage of total generation</t>
+          <t>User-Defined Setting for VRE Max-Scale up (if used)</t>
         </is>
       </c>
       <c r="C359" s="8" t="n"/>
@@ -8313,122 +8647,126 @@
       </c>
       <c r="H359" s="8" t="inlineStr">
         <is>
-          <t>MaxNonVREAsPCOfTotalGen</t>
+          <t>MaxWindSolarScaleup</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="B360" s="8" t="inlineStr">
         <is>
-          <t>Max new investment oil/nucl/ore/bio as a percentage of total generation</t>
-        </is>
-      </c>
-      <c r="C360" s="8" t="n"/>
+          <t>Max renewable scaleup rate setting</t>
+        </is>
+      </c>
+      <c r="C360" s="8" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
       <c r="D360" s="8" t="n"/>
       <c r="E360" s="8" t="n"/>
-      <c r="F360" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G360" s="8" t="n">
-        <v>0.02</v>
+      <c r="F360" s="8" t="inlineStr">
+        <is>
+          <t>CtryDefault*</t>
+        </is>
+      </c>
+      <c r="G360" s="8" t="inlineStr">
+        <is>
+          <t>CtryDefault*</t>
+        </is>
       </c>
       <c r="H360" s="8" t="inlineStr">
         <is>
-          <t>MaxNonNucOreBioAsPCOfTotalGen</t>
+          <t>MaxScaleUpRateCategory</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="B361" s="8" t="inlineStr">
-        <is>
-          <t>User-Defined Setting for VRE Max-Scale up (if used)</t>
-        </is>
-      </c>
-      <c r="C361" s="8" t="n"/>
-      <c r="D361" s="8" t="n"/>
-      <c r="E361" s="8" t="n"/>
-      <c r="F361" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G361" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H361" s="8" t="inlineStr">
-        <is>
-          <t>MaxWindSolarScaleup</t>
+      <c r="B361" s="1" t="inlineStr">
+        <is>
+          <t>More Power Generation Settings</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t>Max renewable scaleup rate setting</t>
-        </is>
-      </c>
-      <c r="C362" s="8" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
+          <t>Use Elasticity Model Power Demand In Engineer Model</t>
+        </is>
+      </c>
+      <c r="C362" s="8" t="n"/>
       <c r="D362" s="8" t="n"/>
       <c r="E362" s="8" t="n"/>
       <c r="F362" s="8" t="inlineStr">
         <is>
-          <t>CtryDefault*</t>
+          <t>No*</t>
         </is>
       </c>
       <c r="G362" s="8" t="inlineStr">
         <is>
-          <t>CtryDefault*</t>
+          <t>No*</t>
         </is>
       </c>
       <c r="H362" s="8" t="inlineStr">
         <is>
-          <t>MaxScaleUpRateCategory</t>
+          <t>UseElasticityModelPowerDemandInEngineerModel</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="B363" s="1" t="inlineStr">
-        <is>
-          <t>More Power Generation Settings</t>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B363" s="8" t="inlineStr">
+        <is>
+          <t>Cost of capital: User-defined, Inc-dep,  or Tech-dep?</t>
+        </is>
+      </c>
+      <c r="C363" s="8" t="n"/>
+      <c r="D363" s="8" t="n"/>
+      <c r="E363" s="8" t="n"/>
+      <c r="F363" s="8" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="G363" s="8" t="inlineStr">
+        <is>
+          <t>Income*</t>
+        </is>
+      </c>
+      <c r="H363" s="8" t="inlineStr">
+        <is>
+          <t>WACCSource</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="B364" s="8" t="inlineStr">
         <is>
-          <t>Use Elasticity Model Power Demand In Engineer Model</t>
+          <t>If Global, what Value?</t>
         </is>
       </c>
       <c r="C364" s="8" t="n"/>
       <c r="D364" s="8" t="n"/>
       <c r="E364" s="8" t="n"/>
-      <c r="F364" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
-      </c>
-      <c r="G364" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
+      <c r="F364" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G364" s="8" t="n">
+        <v>0.075</v>
       </c>
       <c r="H364" s="8" t="inlineStr">
         <is>
-          <t>UseElasticityModelPowerDemandInEngineerModel</t>
+          <t>WACCUserGlobal</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Cost of capital: User-defined, Inc-dep,  or Tech-dep?</t>
+          <t>Renewable Cost Declines</t>
         </is>
       </c>
       <c r="C365" s="8" t="n"/>
@@ -8436,45 +8774,49 @@
       <c r="E365" s="8" t="n"/>
       <c r="F365" s="8" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Medium*</t>
         </is>
       </c>
       <c r="G365" s="8" t="inlineStr">
         <is>
-          <t>Income*</t>
+          <t>Medium*</t>
         </is>
       </c>
       <c r="H365" s="8" t="inlineStr">
         <is>
-          <t>WACCSource</t>
+          <t>RenewableCostDeclineRate</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="B366" s="8" t="inlineStr">
         <is>
-          <t>If Global, what Value?</t>
+          <t>Use Spot Fuel Prices in Engineer Power Model</t>
         </is>
       </c>
       <c r="C366" s="8" t="n"/>
       <c r="D366" s="8" t="n"/>
       <c r="E366" s="8" t="n"/>
-      <c r="F366" s="8" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G366" s="8" t="n">
-        <v>0.075</v>
+      <c r="F366" s="8" t="inlineStr">
+        <is>
+          <t>No*</t>
+        </is>
+      </c>
+      <c r="G366" s="8" t="inlineStr">
+        <is>
+          <t>No*</t>
+        </is>
       </c>
       <c r="H366" s="8" t="inlineStr">
         <is>
-          <t>WACCUserGlobal</t>
+          <t>UseSpotFuelPricesInEngineerModel</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>Renewable Cost Declines</t>
+          <t>Use Additional Coal Intangible Cost</t>
         </is>
       </c>
       <c r="C367" s="8" t="n"/>
@@ -8482,609 +8824,617 @@
       <c r="E367" s="8" t="n"/>
       <c r="F367" s="8" t="inlineStr">
         <is>
-          <t>Medium*</t>
+          <t>Yes*</t>
         </is>
       </c>
       <c r="G367" s="8" t="inlineStr">
         <is>
-          <t>Medium*</t>
+          <t>Yes*</t>
         </is>
       </c>
       <c r="H367" s="8" t="inlineStr">
         <is>
-          <t>RenewableCostDeclineRate</t>
+          <t>AdditionalCoalIntangibleCost</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="8" t="inlineStr">
         <is>
-          <t>Use Spot Fuel Prices in Engineer Power Model</t>
+          <t>Manual Coal Intangible Cost (short term)</t>
         </is>
       </c>
       <c r="C368" s="8" t="n"/>
       <c r="D368" s="8" t="n"/>
       <c r="E368" s="8" t="n"/>
-      <c r="F368" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
-      </c>
-      <c r="G368" s="8" t="inlineStr">
-        <is>
-          <t>No*</t>
-        </is>
+      <c r="F368" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H368" s="8" t="inlineStr">
         <is>
-          <t>UseSpotFuelPricesInEngineerModel</t>
+          <t>ManualCoalIntangibleCostST</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Use Additional Coal Intangible Cost</t>
+          <t>Manual Coal Intangible Cost (long term)</t>
         </is>
       </c>
       <c r="C369" s="8" t="n"/>
       <c r="D369" s="8" t="n"/>
       <c r="E369" s="8" t="n"/>
-      <c r="F369" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
-      </c>
-      <c r="G369" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
+      <c r="F369" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H369" s="8" t="inlineStr">
         <is>
-          <t>AdditionalCoalIntangibleCost</t>
+          <t>ManualCoalIntangibleCostLT</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="B370" s="8" t="inlineStr">
         <is>
-          <t>Manual Coal Intangible Cost (short term)</t>
+          <t>Maximum Coal Capacity Factor</t>
         </is>
       </c>
       <c r="C370" s="8" t="n"/>
       <c r="D370" s="8" t="n"/>
       <c r="E370" s="8" t="n"/>
       <c r="F370" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G370" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H370" s="8" t="inlineStr">
         <is>
-          <t>ManualCoalIntangibleCostST</t>
+          <t>MaximumCoalCF</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Manual Coal Intangible Cost (long term)</t>
+          <t>Maximum Gas Capacity Factor</t>
         </is>
       </c>
       <c r="C371" s="8" t="n"/>
       <c r="D371" s="8" t="n"/>
       <c r="E371" s="8" t="n"/>
       <c r="F371" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G371" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H371" s="8" t="inlineStr">
         <is>
-          <t>ManualCoalIntangibleCostLT</t>
+          <t>MaximumGasCF</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="B372" s="8" t="inlineStr">
         <is>
-          <t>Maximum Coal Capacity Factor</t>
+          <t>Proportion of GHG adjustment passed on to engineer model power demand</t>
         </is>
       </c>
       <c r="C372" s="8" t="n"/>
       <c r="D372" s="8" t="n"/>
       <c r="E372" s="8" t="n"/>
       <c r="F372" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G372" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H372" s="8" t="inlineStr">
         <is>
-          <t>MaximumCoalCF</t>
+          <t>EngineerModelProportionOfCovidFactor</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>Maximum Gas Capacity Factor</t>
+          <t>Override Capacity Factor if below (Wind and Solar)</t>
         </is>
       </c>
       <c r="C373" s="8" t="n"/>
       <c r="D373" s="8" t="n"/>
       <c r="E373" s="8" t="n"/>
       <c r="F373" s="8" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="G373" s="8" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H373" s="8" t="inlineStr">
         <is>
-          <t>MaximumGasCF</t>
+          <t>CFOverrideIfBelowWndSol</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="B374" s="8" t="inlineStr">
         <is>
-          <t>Proportion of GHG adjustment passed on to engineer model power demand</t>
+          <t>Override Capacity Factor if below (Others)</t>
         </is>
       </c>
       <c r="C374" s="8" t="n"/>
       <c r="D374" s="8" t="n"/>
       <c r="E374" s="8" t="n"/>
       <c r="F374" s="8" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G374" s="8" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="H374" s="8" t="inlineStr">
         <is>
-          <t>EngineerModelProportionOfCovidFactor</t>
+          <t>CFOverrideIfBelowFosOth</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>Override Capacity Factor if below (Wind and Solar)</t>
+          <t>Override Capacity Factor if below (All)</t>
         </is>
       </c>
       <c r="C375" s="8" t="n"/>
       <c r="D375" s="8" t="n"/>
       <c r="E375" s="8" t="n"/>
       <c r="F375" s="8" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G375" s="8" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H375" s="8" t="inlineStr">
         <is>
-          <t>CFOverrideIfBelowWndSol</t>
+          <t>CFOverrideIfAbove</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="8" t="inlineStr">
         <is>
-          <t>Override Capacity Factor if below (Others)</t>
+          <t>Proportion of coal capacity that can be retired</t>
         </is>
       </c>
       <c r="C376" s="8" t="n"/>
       <c r="D376" s="8" t="n"/>
       <c r="E376" s="8" t="n"/>
       <c r="F376" s="8" t="n">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="G376" s="8" t="n">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="H376" s="8" t="inlineStr">
         <is>
-          <t>CFOverrideIfBelowFosOth</t>
+          <t>MaxCostBasedEarlyRetirement</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>Override Capacity Factor if below (All)</t>
+          <t>Allow cost-based coal phaseout in baseline?</t>
         </is>
       </c>
       <c r="C377" s="8" t="n"/>
       <c r="D377" s="8" t="n"/>
       <c r="E377" s="8" t="n"/>
-      <c r="F377" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G377" s="8" t="n">
-        <v>1</v>
+      <c r="F377" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G377" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="H377" s="8" t="inlineStr">
         <is>
-          <t>CFOverrideIfAbove</t>
+          <t>EarlyRetirementInBaseline</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="8" t="inlineStr">
         <is>
-          <t>Proportion of coal capacity that can be retired</t>
+          <t>Minimum Thermal Efficiency</t>
         </is>
       </c>
       <c r="C378" s="8" t="n"/>
       <c r="D378" s="8" t="n"/>
       <c r="E378" s="8" t="n"/>
       <c r="F378" s="8" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="G378" s="8" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H378" s="8" t="inlineStr">
         <is>
-          <t>MaxCostBasedEarlyRetirement</t>
+          <t>MinimumThermalEfficiency</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="B379" s="8" t="inlineStr">
-        <is>
-          <t>Allow cost-based coal phaseout in baseline?</t>
-        </is>
-      </c>
-      <c r="C379" s="8" t="n"/>
-      <c r="D379" s="8" t="n"/>
-      <c r="E379" s="8" t="n"/>
-      <c r="F379" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G379" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H379" s="8" t="inlineStr">
-        <is>
-          <t>EarlyRetirementInBaseline</t>
+      <c r="B379" s="1" t="inlineStr">
+        <is>
+          <t>Coal and Gas Power Purchase Agreements</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="8" t="inlineStr">
         <is>
-          <t>Minimum Thermal Efficiency</t>
+          <t>Proportion of PPAs in Coal and Gas Generation</t>
         </is>
       </c>
       <c r="C380" s="8" t="n"/>
       <c r="D380" s="8" t="n"/>
       <c r="E380" s="8" t="n"/>
       <c r="F380" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G380" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H380" s="8" t="inlineStr">
         <is>
-          <t>MinimumThermalEfficiency</t>
+          <t>PPAProportionCoalGas</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="B381" s="1" t="inlineStr">
-        <is>
-          <t>Coal and Gas Power Purchase Agreements</t>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Phase out any coal and gas PPAs? (Baseline)</t>
+        </is>
+      </c>
+      <c r="C381" s="8" t="n"/>
+      <c r="D381" s="8" t="n"/>
+      <c r="E381" s="8" t="n"/>
+      <c r="F381" s="8" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
+      </c>
+      <c r="G381" s="8" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
+      </c>
+      <c r="H381" s="8" t="inlineStr">
+        <is>
+          <t>PhaseOutCoalAndGasPPAsBaseline</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="B382" s="8" t="inlineStr">
         <is>
-          <t>Proportion of PPAs in Coal and Gas Generation</t>
+          <t>Phase out any coal and gas PPAs? (Policy)</t>
         </is>
       </c>
       <c r="C382" s="8" t="n"/>
       <c r="D382" s="8" t="n"/>
       <c r="E382" s="8" t="n"/>
-      <c r="F382" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G382" s="8" t="n">
-        <v>0</v>
+      <c r="F382" s="8" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
+      </c>
+      <c r="G382" s="8" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
       </c>
       <c r="H382" s="8" t="inlineStr">
         <is>
-          <t>PPAProportionCoalGas</t>
+          <t>PhaseOutCoalAndGasPPAsPolicy</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Phase out any coal and gas PPAs? (Baseline)</t>
+          <t>Phase begins when?</t>
         </is>
       </c>
       <c r="C383" s="8" t="n"/>
       <c r="D383" s="8" t="n"/>
       <c r="E383" s="8" t="n"/>
-      <c r="F383" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
-      </c>
-      <c r="G383" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
+      <c r="F383" s="8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G383" s="8" t="n">
+        <v>2027</v>
       </c>
       <c r="H383" s="8" t="inlineStr">
         <is>
-          <t>PhaseOutCoalAndGasPPAsBaseline</t>
+          <t>YearPPACoalGas</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="B384" s="8" t="inlineStr">
         <is>
-          <t>Phase out any coal and gas PPAs? (Policy)</t>
+          <t>Phase out coal and gas PPAs over n years?</t>
         </is>
       </c>
       <c r="C384" s="8" t="n"/>
       <c r="D384" s="8" t="n"/>
       <c r="E384" s="8" t="n"/>
-      <c r="F384" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
-      </c>
-      <c r="G384" s="8" t="inlineStr">
-        <is>
-          <t>Yes*</t>
-        </is>
+      <c r="F384" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G384" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="H384" s="8" t="inlineStr">
         <is>
-          <t>PhaseOutCoalAndGasPPAsPolicy</t>
+          <t>YearsToPhaseOutPPAs</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="B385" s="8" t="inlineStr">
-        <is>
-          <t>Phase begins when?</t>
-        </is>
-      </c>
-      <c r="C385" s="8" t="n"/>
-      <c r="D385" s="8" t="n"/>
-      <c r="E385" s="8" t="n"/>
-      <c r="F385" s="8" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G385" s="8" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H385" s="8" t="inlineStr">
-        <is>
-          <t>YearPPACoalGas</t>
+      <c r="B385" s="1" t="inlineStr">
+        <is>
+          <t>Short Term Storage Parameters</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="B386" s="8" t="inlineStr">
         <is>
-          <t>Phase out coal and gas PPAs over n years?</t>
-        </is>
-      </c>
-      <c r="C386" s="8" t="n"/>
+          <t>Percent allocation of ST storage costs to VRE</t>
+        </is>
+      </c>
+      <c r="C386" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D386" s="8" t="n"/>
       <c r="E386" s="8" t="n"/>
       <c r="F386" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G386" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H386" s="8" t="inlineStr">
         <is>
-          <t>YearsToPhaseOutPPAs</t>
+          <t>AllocateSTStorageToVRE</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="B387" s="1" t="inlineStr">
-        <is>
-          <t>Short Term Storage Parameters</t>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>Total hours short term strorage for 100% VRE</t>
+        </is>
+      </c>
+      <c r="C387" s="8" t="n"/>
+      <c r="D387" s="8" t="n"/>
+      <c r="E387" s="8" t="n"/>
+      <c r="F387" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G387" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H387" s="8" t="inlineStr">
+        <is>
+          <t>TotalHoursStorageFor100pcVRE</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="B388" s="8" t="inlineStr">
         <is>
-          <t>Percent allocation of ST storage costs to VRE</t>
-        </is>
-      </c>
-      <c r="C388" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>kwh storage to kw interface ratio (hours)</t>
+        </is>
+      </c>
+      <c r="C388" s="8" t="n"/>
       <c r="D388" s="8" t="n"/>
       <c r="E388" s="8" t="n"/>
       <c r="F388" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G388" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H388" s="8" t="inlineStr">
         <is>
-          <t>AllocateSTStorageToVRE</t>
+          <t>StorageToInterfaceRatioSTStorage</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="B389" s="8" t="inlineStr">
-        <is>
-          <t>Total hours short term strorage for 100% VRE</t>
-        </is>
-      </c>
-      <c r="C389" s="8" t="n"/>
-      <c r="D389" s="8" t="n"/>
-      <c r="E389" s="8" t="n"/>
-      <c r="F389" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G389" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H389" s="8" t="inlineStr">
-        <is>
-          <t>TotalHoursStorageFor100pcVRE</t>
+      <c r="B389" s="1" t="inlineStr">
+        <is>
+          <t>Long Term Storage Parameters</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="B390" s="8" t="inlineStr">
         <is>
-          <t>kwh storage to kw interface ratio (hours)</t>
+          <t>Percent allocation of LT storage costs to VRE</t>
         </is>
       </c>
       <c r="C390" s="8" t="n"/>
       <c r="D390" s="8" t="n"/>
       <c r="E390" s="8" t="n"/>
       <c r="F390" s="8" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="G390" s="8" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="H390" s="8" t="inlineStr">
         <is>
-          <t>StorageToInterfaceRatioSTStorage</t>
+          <t>AllocateLTStorageToVRE</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="B391" s="1" t="inlineStr">
-        <is>
-          <t>Long Term Storage Parameters</t>
+      <c r="B391" s="8" t="inlineStr">
+        <is>
+          <t>Starting point of long term storage requirement (%VRE)</t>
+        </is>
+      </c>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D391" s="8" t="n"/>
+      <c r="E391" s="8" t="n"/>
+      <c r="F391" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G391" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H391" s="8" t="inlineStr">
+        <is>
+          <t>StartingPointWhenLTStorageIsNeeded</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="B392" s="8" t="inlineStr">
         <is>
-          <t>Percent allocation of LT storage costs to VRE</t>
-        </is>
-      </c>
-      <c r="C392" s="8" t="n"/>
+          <t>GW electrolyzer per Gwy/y for 100% VRE (%)</t>
+        </is>
+      </c>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D392" s="8" t="n"/>
       <c r="E392" s="8" t="n"/>
       <c r="F392" s="8" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="G392" s="8" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H392" s="8" t="inlineStr">
         <is>
-          <t>AllocateLTStorageToVRE</t>
+          <t>LongTermStorageFor100pcVRE</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="B393" s="8" t="inlineStr">
         <is>
-          <t>Starting point of long term storage requirement (%VRE)</t>
-        </is>
-      </c>
-      <c r="C393" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Storage hours for LT storage</t>
+        </is>
+      </c>
+      <c r="C393" s="8" t="n"/>
       <c r="D393" s="8" t="n"/>
       <c r="E393" s="8" t="n"/>
       <c r="F393" s="8" t="n">
-        <v>0.75</v>
+        <v>1000</v>
       </c>
       <c r="G393" s="8" t="n">
-        <v>0.75</v>
+        <v>1000</v>
       </c>
       <c r="H393" s="8" t="inlineStr">
         <is>
-          <t>StartingPointWhenLTStorageIsNeeded</t>
+          <t>StorageHoursForLTStorage</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="B394" s="8" t="inlineStr">
-        <is>
-          <t>GW electrolyzer per Gwy/y for 100% VRE (%)</t>
-        </is>
-      </c>
-      <c r="C394" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D394" s="8" t="n"/>
-      <c r="E394" s="8" t="n"/>
-      <c r="F394" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G394" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H394" s="8" t="inlineStr">
-        <is>
-          <t>LongTermStorageFor100pcVRE</t>
+      <c r="B394" s="1" t="inlineStr">
+        <is>
+          <t>Allowed New Investments Override if selected</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="B395" s="8" t="inlineStr">
         <is>
-          <t>Storage hours for LT storage</t>
-        </is>
-      </c>
-      <c r="C395" s="8" t="n"/>
+          <t>Coal - New Investment Override</t>
+        </is>
+      </c>
+      <c r="C395" s="8" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
       <c r="D395" s="8" t="n"/>
       <c r="E395" s="8" t="n"/>
-      <c r="F395" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G395" s="8" t="n">
-        <v>1000</v>
+      <c r="F395" s="8" t="inlineStr">
+        <is>
+          <t>If Present*</t>
+        </is>
+      </c>
+      <c r="G395" s="8" t="inlineStr">
+        <is>
+          <t>If Present*</t>
+        </is>
       </c>
       <c r="H395" s="8" t="inlineStr">
         <is>
-          <t>StorageHoursForLTStorage</t>
+          <t>NewInvCoa</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="B396" s="1" t="inlineStr">
-        <is>
-          <t>Allowed New Investments Override if selected</t>
+      <c r="B396" s="8" t="inlineStr">
+        <is>
+          <t>Natural gas - New Investment Override</t>
+        </is>
+      </c>
+      <c r="C396" s="8" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="D396" s="8" t="n"/>
+      <c r="E396" s="8" t="n"/>
+      <c r="F396" s="8" t="inlineStr">
+        <is>
+          <t>If Present*</t>
+        </is>
+      </c>
+      <c r="G396" s="8" t="inlineStr">
+        <is>
+          <t>If Present*</t>
+        </is>
+      </c>
+      <c r="H396" s="8" t="inlineStr">
+        <is>
+          <t>NewInvNga</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Coal - New Investment Override</t>
+          <t>Oil - New Investment Override</t>
         </is>
       </c>
       <c r="C397" s="8" t="inlineStr">
@@ -9106,14 +9456,14 @@
       </c>
       <c r="H397" s="8" t="inlineStr">
         <is>
-          <t>NewInvCoa</t>
+          <t>NewInvOil</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="B398" s="8" t="inlineStr">
         <is>
-          <t>Natural gas - New Investment Override</t>
+          <t>Nuclear - New Investment Override</t>
         </is>
       </c>
       <c r="C398" s="8" t="inlineStr">
@@ -9135,14 +9485,14 @@
       </c>
       <c r="H398" s="8" t="inlineStr">
         <is>
-          <t>NewInvNga</t>
+          <t>NewInvNuc</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Oil - New Investment Override</t>
+          <t>Wind - New Investment Override</t>
         </is>
       </c>
       <c r="C399" s="8" t="inlineStr">
@@ -9154,24 +9504,24 @@
       <c r="E399" s="8" t="n"/>
       <c r="F399" s="8" t="inlineStr">
         <is>
-          <t>If Present*</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G399" s="8" t="inlineStr">
         <is>
-          <t>If Present*</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H399" s="8" t="inlineStr">
         <is>
-          <t>NewInvOil</t>
+          <t>NewInvWnd</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="8" t="inlineStr">
         <is>
-          <t>Nuclear - New Investment Override</t>
+          <t>Solar - New Investment Override</t>
         </is>
       </c>
       <c r="C400" s="8" t="inlineStr">
@@ -9183,24 +9533,24 @@
       <c r="E400" s="8" t="n"/>
       <c r="F400" s="8" t="inlineStr">
         <is>
-          <t>If Present*</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G400" s="8" t="inlineStr">
         <is>
-          <t>If Present*</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H400" s="8" t="inlineStr">
         <is>
-          <t>NewInvNuc</t>
+          <t>NewInvSol</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Wind - New Investment Override</t>
+          <t>Hydro - New Investment Override</t>
         </is>
       </c>
       <c r="C401" s="8" t="inlineStr">
@@ -9212,24 +9562,24 @@
       <c r="E401" s="8" t="n"/>
       <c r="F401" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>If Present*</t>
         </is>
       </c>
       <c r="G401" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>If Present*</t>
         </is>
       </c>
       <c r="H401" s="8" t="inlineStr">
         <is>
-          <t>NewInvWnd</t>
+          <t>NewInvHyd</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="B402" s="8" t="inlineStr">
         <is>
-          <t>Solar - New Investment Override</t>
+          <t>Other renewables - New Investment Override</t>
         </is>
       </c>
       <c r="C402" s="8" t="inlineStr">
@@ -9241,24 +9591,24 @@
       <c r="E402" s="8" t="n"/>
       <c r="F402" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>If Present*</t>
         </is>
       </c>
       <c r="G402" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>If Present*</t>
         </is>
       </c>
       <c r="H402" s="8" t="inlineStr">
         <is>
-          <t>NewInvSol</t>
+          <t>NewInvOre</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>Hydro - New Investment Override</t>
+          <t>Biomass - New Investment Override</t>
         </is>
       </c>
       <c r="C403" s="8" t="inlineStr">
@@ -9280,79 +9630,71 @@
       </c>
       <c r="H403" s="8" t="inlineStr">
         <is>
-          <t>NewInvHyd</t>
+          <t>NewInvBio</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="B404" s="8" t="inlineStr">
-        <is>
-          <t>Other renewables - New Investment Override</t>
-        </is>
-      </c>
-      <c r="C404" s="8" t="inlineStr">
-        <is>
-          <t>Switch</t>
-        </is>
-      </c>
-      <c r="D404" s="8" t="n"/>
-      <c r="E404" s="8" t="n"/>
-      <c r="F404" s="8" t="inlineStr">
-        <is>
-          <t>If Present*</t>
-        </is>
-      </c>
-      <c r="G404" s="8" t="inlineStr">
-        <is>
-          <t>If Present*</t>
-        </is>
-      </c>
-      <c r="H404" s="8" t="inlineStr">
-        <is>
-          <t>NewInvOre</t>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Allowed New Investments (Date of Coming Online)</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>Biomass - New Investment Override</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C405" s="8" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="D405" s="8" t="n"/>
       <c r="E405" s="8" t="n"/>
-      <c r="F405" s="8" t="inlineStr">
-        <is>
-          <t>If Present*</t>
-        </is>
-      </c>
-      <c r="G405" s="8" t="inlineStr">
-        <is>
-          <t>If Present*</t>
-        </is>
+      <c r="F405" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G405" s="8" t="n">
+        <v>2022</v>
       </c>
       <c r="H405" s="8" t="inlineStr">
         <is>
-          <t>NewInvBio</t>
+          <t>NewInvCoaYear</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Allowed New Investments (Date of Coming Online)</t>
+      <c r="B406" s="8" t="inlineStr">
+        <is>
+          <t>Natural gas</t>
+        </is>
+      </c>
+      <c r="C406" s="8" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D406" s="8" t="n"/>
+      <c r="E406" s="8" t="n"/>
+      <c r="F406" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G406" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H406" s="8" t="inlineStr">
+        <is>
+          <t>NewInvNgaYear</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="C407" s="8" t="inlineStr">
@@ -9370,14 +9712,14 @@
       </c>
       <c r="H407" s="8" t="inlineStr">
         <is>
-          <t>NewInvCoaYear</t>
+          <t>NewInvOilYear</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="B408" s="8" t="inlineStr">
         <is>
-          <t>Natural gas</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C408" s="8" t="inlineStr">
@@ -9388,21 +9730,21 @@
       <c r="D408" s="8" t="n"/>
       <c r="E408" s="8" t="n"/>
       <c r="F408" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="G408" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="H408" s="8" t="inlineStr">
         <is>
-          <t>NewInvNgaYear</t>
+          <t>NewInvNucYear</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="C409" s="8" t="inlineStr">
@@ -9420,14 +9762,14 @@
       </c>
       <c r="H409" s="8" t="inlineStr">
         <is>
-          <t>NewInvOilYear</t>
+          <t>NewInvWndYear</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="B410" s="8" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="C410" s="8" t="inlineStr">
@@ -9438,21 +9780,21 @@
       <c r="D410" s="8" t="n"/>
       <c r="E410" s="8" t="n"/>
       <c r="F410" s="8" t="n">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="G410" s="8" t="n">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="H410" s="8" t="inlineStr">
         <is>
-          <t>NewInvNucYear</t>
+          <t>NewInvSolYear</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="C411" s="8" t="inlineStr">
@@ -9463,21 +9805,21 @@
       <c r="D411" s="8" t="n"/>
       <c r="E411" s="8" t="n"/>
       <c r="F411" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="G411" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="H411" s="8" t="inlineStr">
         <is>
-          <t>NewInvWndYear</t>
+          <t>NewInvHydYear</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="B412" s="8" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Other renewables</t>
         </is>
       </c>
       <c r="C412" s="8" t="inlineStr">
@@ -9488,21 +9830,21 @@
       <c r="D412" s="8" t="n"/>
       <c r="E412" s="8" t="n"/>
       <c r="F412" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="G412" s="8" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="H412" s="8" t="inlineStr">
         <is>
-          <t>NewInvSolYear</t>
+          <t>NewInvOreYear</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="C413" s="8" t="inlineStr">
@@ -9513,62 +9855,12 @@
       <c r="D413" s="8" t="n"/>
       <c r="E413" s="8" t="n"/>
       <c r="F413" s="8" t="n">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="G413" s="8" t="n">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="H413" s="8" t="inlineStr">
-        <is>
-          <t>NewInvHydYear</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="B414" s="8" t="inlineStr">
-        <is>
-          <t>Other renewables</t>
-        </is>
-      </c>
-      <c r="C414" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D414" s="8" t="n"/>
-      <c r="E414" s="8" t="n"/>
-      <c r="F414" s="8" t="n">
-        <v>2030</v>
-      </c>
-      <c r="G414" s="8" t="n">
-        <v>2030</v>
-      </c>
-      <c r="H414" s="8" t="inlineStr">
-        <is>
-          <t>NewInvOreYear</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="B415" s="8" t="inlineStr">
-        <is>
-          <t>Biomass</t>
-        </is>
-      </c>
-      <c r="C415" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D415" s="8" t="n"/>
-      <c r="E415" s="8" t="n"/>
-      <c r="F415" s="8" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G415" s="8" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H415" s="8" t="inlineStr">
         <is>
           <t>NewInvBioYear</t>
         </is>
